--- a/results/Int All Data 0.1/Rando_8_permute.xlsx
+++ b/results/Int All Data 0.1/Rando_8_permute.xlsx
@@ -440,617 +440,617 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.847266881028939</v>
+        <v>0.8688102893890675</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8514469453376206</v>
+        <v>0.8993569131832797</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8514469453376206</v>
+        <v>0.8890675241157556</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8491961414790996</v>
+        <v>0.8916398713826367</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8491961414790996</v>
+        <v>0.9003215434083601</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8633440514469453</v>
+        <v>0.9006430868167203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8485530546623794</v>
+        <v>0.884887459807074</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8553054662379421</v>
+        <v>0.9045016077170418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8659163987138263</v>
+        <v>0.8855305466237942</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8681672025723473</v>
+        <v>0.8855305466237942</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.852411575562701</v>
+        <v>0.8855305466237942</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8527331189710611</v>
+        <v>0.9213813927742915</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8549839228295819</v>
+        <v>0.9181659586906902</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8504823151125402</v>
+        <v>0.9212193771884543</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8488745980707395</v>
+        <v>0.9260425283138563</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8501607717041801</v>
+        <v>0.9302225926225378</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8469453376205788</v>
+        <v>0.9302225926225378</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8453376205787781</v>
+        <v>0.9323138686585358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8466237942122187</v>
+        <v>0.9360103739730201</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8485530546623794</v>
+        <v>0.9364939329672175</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8501607717041801</v>
+        <v>0.9364939329672175</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8707395498392283</v>
+        <v>0.9323138686585358</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.87491961414791</v>
+        <v>0.9437274157736633</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8881028938906752</v>
+        <v>0.9430843289569431</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8932475884244373</v>
+        <v>0.9372965476064608</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8938906752411575</v>
+        <v>0.9372965476064608</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8935691318327974</v>
+        <v>0.9319898374868615</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8935691318327974</v>
+        <v>0.933276011120302</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8926045016077171</v>
+        <v>0.9337595701144993</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.892282958199357</v>
+        <v>0.9281313165865399</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8832797427652733</v>
+        <v>0.9210573616026172</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.884887459807074</v>
+        <v>0.9176774241698644</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8797427652733119</v>
+        <v>0.8715421644784715</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.880064308681672</v>
+        <v>0.8715421644784715</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8784565916398714</v>
+        <v>0.8715421644784715</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8781350482315112</v>
+        <v>0.870255990845031</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8784565916398714</v>
+        <v>0.8696129040283107</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8794212218649518</v>
+        <v>0.8705775342533911</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8790996784565916</v>
+        <v>0.8710610932475884</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8700964630225081</v>
+        <v>0.9135048231511254</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8694533762057878</v>
+        <v>0.9186495176848875</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8382636655948553</v>
+        <v>0.9045016077170418</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8385852090032154</v>
+        <v>0.9041800643086817</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8498392282958199</v>
+        <v>0.9045016077170418</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8607717041800643</v>
+        <v>0.8885839651215584</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8565916398713826</v>
+        <v>0.8882624217131982</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8819885936052044</v>
+        <v>0.8831177271794362</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8861686579138861</v>
+        <v>0.8845634286353996</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8859966912747921</v>
+        <v>0.8872953037248037</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8863207224464664</v>
+        <v>0.8872953037248037</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8980533252066398</v>
+        <v>0.8776490014739997</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8980533252066398</v>
+        <v>0.8779705448823598</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9086518188659531</v>
+        <v>0.8853635555113286</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9073780840490836</v>
+        <v>0.8807024199717639</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9097909034934416</v>
+        <v>0.9025673717402527</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9210449227860462</v>
+        <v>0.9017622693376952</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9075400996349208</v>
+        <v>0.9017622693376952</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.9093098322625586</v>
+        <v>0.9049801911846107</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9085047298600011</v>
+        <v>0.9279668132373886</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9068970128182005</v>
+        <v>0.9307011760901067</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.90674494828562</v>
+        <v>0.931344262906827</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.937286596553204</v>
+        <v>0.9374510999023553</v>
       </c>
     </row>
     <row r="64">
@@ -1060,647 +1060,647 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.949667261656726</v>
+        <v>0.9327924521261047</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.9107654847717788</v>
+        <v>0.9257184971421819</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.906263877054737</v>
+        <v>0.9257184971421819</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.9117301149968592</v>
+        <v>0.9408285495717937</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.9107654847717788</v>
+        <v>0.9530347602729077</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.861247799884319</v>
+        <v>0.9476832704136529</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8641416905595601</v>
+        <v>0.9515592056571738</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8686432982766019</v>
+        <v>0.9515592056571738</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8564246487589171</v>
+        <v>0.9439942283891111</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8593185394341583</v>
+        <v>0.9439942283891111</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.848707606958274</v>
+        <v>0.9447993307916684</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8448490860579525</v>
+        <v>0.9475560835142145</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8056207902380168</v>
+        <v>0.9477180991000516</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7953338889338069</v>
+        <v>0.9496423840235839</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.793404628483646</v>
+        <v>0.9439967161524253</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7950123455254468</v>
+        <v>0.9422319590514159</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7927615416669258</v>
+        <v>0.9436776605073793</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8162342104772151</v>
+        <v>0.9420699434655786</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8477429767331937</v>
+        <v>0.935170442884064</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8562626331730798</v>
+        <v>0.9359680819966789</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8700865119692514</v>
+        <v>0.9356465385883187</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8723373158277722</v>
+        <v>0.9390165249678145</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.872015772419412</v>
+        <v>0.9380469192161058</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.8737855050470498</v>
+        <v>0.9344999906708875</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8850320610497118</v>
+        <v>0.9265985434145796</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8368105008489493</v>
+        <v>0.9322491868123667</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8379346588965526</v>
+        <v>0.9309580376522978</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8213714417210347</v>
+        <v>0.9279071069178478</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.814140446677903</v>
+        <v>0.9110447362037976</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.8065903959897256</v>
+        <v>0.9110546872570544</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8245221939584668</v>
+        <v>0.9110546872570544</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8245221939584668</v>
+        <v>0.9137865623464583</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8245221939584668</v>
+        <v>0.9147636313881098</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.8516764415033553</v>
+        <v>0.9058751640368936</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.856591950841797</v>
+        <v>0.9094146292921692</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8493833456684932</v>
+        <v>0.9111918252097495</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.8586583492446529</v>
+        <v>0.9054040438592672</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.8243803914495575</v>
+        <v>0.902188609775666</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8127252203225386</v>
+        <v>0.8989657124021221</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.8642439998258565</v>
+        <v>0.8925398197615479</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.8642439998258565</v>
+        <v>0.8938284811583026</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.8435106693949138</v>
+        <v>0.8963983406618694</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8435106693949138</v>
+        <v>0.8972034430644269</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.8375782868017937</v>
+        <v>0.8851418336059507</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.8375782868017937</v>
+        <v>0.7838929764222232</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.8599168465112229</v>
+        <v>0.7802039343976814</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.8626512093639411</v>
+        <v>0.7885640630150448</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.8303522672852905</v>
+        <v>0.7933872141404467</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.8235998557097277</v>
+        <v>0.7628430781095487</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.8608590868664755</v>
+        <v>0.7628430781095487</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.8608590868664755</v>
+        <v>0.7605897864877136</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.8487999651713136</v>
+        <v>0.7593011250909588</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.8614723205234254</v>
+        <v>0.7609088421327594</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.7873655830384296</v>
+        <v>0.7790723130601355</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.7573849253981976</v>
+        <v>0.7700690976260518</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.7601814823337707</v>
+        <v>0.7742466741714193</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.7590672753394242</v>
+        <v>0.7782647228942638</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.7590672753394242</v>
+        <v>0.7539869516814171</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.7614676559672113</v>
+        <v>0.7570428579424953</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.7777764993438524</v>
+        <v>0.7744062019939423</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.7582649716705953</v>
+        <v>0.7641193006897324</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.7549049363443563</v>
+        <v>0.7228047043604271</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.7510339766274636</v>
+        <v>0.7211944995553123</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.6512413938937849</v>
+        <v>0.7290710691784783</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6065670732086549</v>
+        <v>0.7126773308787402</v>
       </c>
     </row>
     <row r="129">
@@ -1710,277 +1710,277 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6065670732086549</v>
+        <v>0.7062464627115377</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6136285893760067</v>
+        <v>0.7062464627115377</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6134640860268554</v>
+        <v>0.7086194779428685</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5487446124375727</v>
+        <v>0.7393131907430327</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5487446124375727</v>
+        <v>0.7381790816421725</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5427848644479965</v>
+        <v>0.7381790816421725</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5072882135993582</v>
+        <v>0.7280019528942017</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5072882135993582</v>
+        <v>0.7280019528942017</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5030957104741055</v>
+        <v>0.7280019528942017</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4924922412881638</v>
+        <v>0.7271968504916442</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.492813784696524</v>
+        <v>0.7424689185070932</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4974898468159739</v>
+        <v>0.5678916827852998</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.497811390224334</v>
+        <v>0.5682132261936599</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5019989178229584</v>
+        <v>0.5508349555623278</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4952465062473956</v>
+        <v>0.5690080665725463</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4963731520583132</v>
+        <v>0.559491438984495</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.497023702164976</v>
+        <v>0.5526619067461922</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.501527797645332</v>
+        <v>0.5536290247345867</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4859242351682661</v>
+        <v>0.6126182465000281</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4906600036072568</v>
+        <v>0.580521435190656</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4867965071803069</v>
+        <v>0.4724110158159552</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4867965071803069</v>
+        <v>0.4425398197615479</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4867965071803069</v>
+        <v>0.5594357752803398</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4806424026818088</v>
+        <v>0.522949305603065</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4809561718298121</v>
+        <v>0.5225506415319646</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4809561718298121</v>
+        <v>0.5235127839937308</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4953208281764073</v>
+        <v>0.5205641625255774</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4939124431701568</v>
+        <v>0.501929571420575</v>
       </c>
     </row>
   </sheetData>
